--- a/test/appium_tests/test_file/test_register.xlsx
+++ b/test/appium_tests/test_file/test_register.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\University\KYII_NAM_3\KTPM\code_test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nam3\hocky2\kiemthu_giuaky\app_music\test\appium_tests\test_file\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B8CCFF-DFA0-486C-9CC2-7EDA08706BF1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF08C169-5D38-40CA-9F44-532B3B51700A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="40">
   <si>
     <t>FirstName</t>
   </si>
@@ -45,21 +45,12 @@
     <t>Expected Result</t>
   </si>
   <si>
-    <t>Vuong</t>
-  </si>
-  <si>
     <t xml:space="preserve">Test Case </t>
   </si>
   <si>
-    <t>Hiep</t>
-  </si>
-  <si>
     <t>0339420356</t>
   </si>
   <si>
-    <t>quochiep1610@gmail.com</t>
-  </si>
-  <si>
     <t>Thành Công</t>
   </si>
   <si>
@@ -84,9 +75,6 @@
     <t>0339420354</t>
   </si>
   <si>
-    <t>0339420355</t>
-  </si>
-  <si>
     <t>Test 1</t>
   </si>
   <si>
@@ -123,18 +111,6 @@
     <t>Test 10</t>
   </si>
   <si>
-    <t>Số điện thoại không hợp lệ</t>
-  </si>
-  <si>
-    <t>quochiep@gmail.com</t>
-  </si>
-  <si>
-    <t>quochiepgmail.com</t>
-  </si>
-  <si>
-    <t>Test 11</t>
-  </si>
-  <si>
     <t>0339420361</t>
   </si>
   <si>
@@ -151,6 +127,24 @@
   </si>
   <si>
     <t>Password không được bỏ trống</t>
+  </si>
+  <si>
+    <t>blackoden@gmail.com</t>
+  </si>
+  <si>
+    <t>Khai</t>
+  </si>
+  <si>
+    <t>Black</t>
+  </si>
+  <si>
+    <t>khai@gmail.com</t>
+  </si>
+  <si>
+    <t>blackoden.com</t>
+  </si>
+  <si>
+    <t>0339420353</t>
   </si>
 </sst>
 </file>
@@ -227,7 +221,7 @@
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
@@ -235,7 +229,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -532,7 +526,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -556,253 +550,238 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F2" s="3">
         <v>123456</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3"/>
       <c r="D3" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F3" s="3">
         <v>123456</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F4" s="3">
         <v>123456</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="3">
         <v>123456</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="F7" s="3">
         <v>123456</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F8" s="3">
         <v>123456</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D9" s="6">
-        <v>123</v>
+        <v>36</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="F9" s="3">
-        <v>123456</v>
+        <v>123455</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E10" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F10" s="3">
-        <v>123456</v>
+        <v>11</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="7">
+        <v>123455</v>
+      </c>
+      <c r="G11" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="3">
-        <v>12</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="7">
-        <v>123456</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>11</v>
-      </c>
+      <c r="A12" s="3"/>
+      <c r="B12" s="3"/>
+      <c r="C12" s="3"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="E3" r:id="rId1" xr:uid="{BA409608-C7C4-47D3-ACD0-39957439E1DA}"/>
-    <hyperlink ref="E2" r:id="rId2" xr:uid="{7FFBB641-62EA-47CB-821D-114C15AF1B76}"/>
-    <hyperlink ref="E7" r:id="rId3" xr:uid="{AC06C32B-C6C9-4899-B90A-744F1F0F2E6E}"/>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{7FFBB641-62EA-47CB-821D-114C15AF1B76}"/>
+    <hyperlink ref="E7" r:id="rId2" xr:uid="{49C9B917-5E3D-4D3F-980A-74E968578CC6}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
